--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="REFLECT Mapped" sheetId="1" r:id="rId1"/>
+    <sheet name="SHEET1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
   <si>
     <t>location</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>HS_in_mmol/L</t>
+  </si>
+  <si>
+    <t>Database_number</t>
   </si>
   <si>
     <t>Weixi–Qiaohou Fault</t>
@@ -497,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="21.7109375" customWidth="1"/>
@@ -518,9 +521,10 @@
     <col min="25" max="27" width="20.7109375" customWidth="1"/>
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,13 +612,16 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>26.4357</v>
@@ -661,13 +668,16 @@
       <c r="AA2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AD2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>26.4357</v>
@@ -714,13 +724,16 @@
       <c r="AA3">
         <v>0.0691880802968797</v>
       </c>
-    </row>
-    <row r="4" spans="1:29">
+      <c r="AD3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>26.4357</v>
@@ -767,13 +780,16 @@
       <c r="AA4">
         <v>0.0419321698768968</v>
       </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AD4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>26.4357</v>
@@ -832,13 +848,16 @@
       <c r="AA5">
         <v>0.000806387882248</v>
       </c>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="AD5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>26.2537</v>
@@ -885,13 +904,16 @@
       <c r="AA6">
         <v>0.0477381626290825</v>
       </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AD6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>26.2537</v>
@@ -935,13 +957,16 @@
       <c r="AA7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>26.2537</v>
@@ -988,13 +1013,16 @@
       <c r="AA8">
         <v>0.0567697069102603</v>
       </c>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="AD8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>26.2537</v>
@@ -1041,13 +1069,16 @@
       <c r="AA9">
         <v>0.0567697069102603</v>
       </c>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="AD9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>26.2537</v>
@@ -1094,13 +1125,16 @@
       <c r="AA10">
         <v>0.064188475426942</v>
       </c>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>26.2537</v>
@@ -1147,13 +1181,16 @@
       <c r="AA11">
         <v>0.050802436581625</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>26.2537</v>
@@ -1209,13 +1246,16 @@
       <c r="AA12">
         <v>0.0683816924146317</v>
       </c>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>26.2519</v>
@@ -1262,13 +1302,16 @@
       <c r="AA13">
         <v>0.0069349357873329</v>
       </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14">
         <v>26.2519</v>
@@ -1315,13 +1358,16 @@
       <c r="AA14">
         <v>0.0443513335236408</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15">
         <v>26.2519</v>
@@ -1368,13 +1414,16 @@
       <c r="AA15">
         <v>0.0408032268417496</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16">
         <v>26.2519</v>
@@ -1433,13 +1482,16 @@
       <c r="AA16">
         <v>0.0012902206115968</v>
       </c>
-    </row>
-    <row r="17" spans="1:27">
+      <c r="AD16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17">
         <v>26.2392</v>
@@ -1483,13 +1535,16 @@
       <c r="AA17">
         <v>0.0114327577336629</v>
       </c>
-    </row>
-    <row r="18" spans="1:27">
+      <c r="AD17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>26.2392</v>
@@ -1536,13 +1591,16 @@
       <c r="AA18">
         <v>0.0193533091739523</v>
       </c>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="AD18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>26.2392</v>
@@ -1589,13 +1647,16 @@
       <c r="AA19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:27">
+      <c r="AD19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20">
         <v>26.2392</v>
@@ -1642,13 +1703,16 @@
       <c r="AA20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:27">
+      <c r="AD20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21">
         <v>26.2392</v>
@@ -1695,13 +1759,16 @@
       <c r="AA21">
         <v>0.0208048073619988</v>
       </c>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="AD21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22">
         <v>26.2392</v>
@@ -1748,13 +1815,16 @@
       <c r="AA22">
         <v>0.0237078037380916</v>
       </c>
-    </row>
-    <row r="23" spans="1:27">
+      <c r="AD22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>26.2392</v>
@@ -1813,13 +1883,16 @@
       <c r="AA23">
         <v>0.0009676654586976</v>
       </c>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="AD23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24">
         <v>26.0843</v>
@@ -1863,13 +1936,16 @@
       <c r="AA24">
         <v>3.890498976693777</v>
       </c>
-    </row>
-    <row r="25" spans="1:27">
+      <c r="AD24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25">
         <v>26.0843</v>
@@ -1916,13 +1992,16 @@
       <c r="AA25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:27">
+      <c r="AD25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C26">
         <v>26.0843</v>
@@ -1969,13 +2048,16 @@
       <c r="AA26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:27">
+      <c r="AD26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>26.0843</v>
@@ -2022,13 +2104,16 @@
       <c r="AA27">
         <v>0.0012902206115968</v>
       </c>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="AD27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <v>26.0843</v>
@@ -2087,13 +2172,16 @@
       <c r="AA28">
         <v>0.000806387882248</v>
       </c>
-    </row>
-    <row r="29" spans="1:27">
+      <c r="AD28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <v>25.8047</v>
@@ -2140,13 +2228,16 @@
       <c r="AA29">
         <v>0.0443513335236408</v>
       </c>
-    </row>
-    <row r="30" spans="1:27">
+      <c r="AD29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30">
         <v>25.8047</v>
@@ -2193,13 +2284,16 @@
       <c r="AA30">
         <v>0.010966875198573</v>
       </c>
-    </row>
-    <row r="31" spans="1:27">
+      <c r="AD30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <v>25.8047</v>
@@ -2246,13 +2340,16 @@
       <c r="AA31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:27">
+      <c r="AD31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32">
         <v>25.8047</v>
@@ -2299,13 +2396,16 @@
       <c r="AA32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:27">
+      <c r="AD32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33">
         <v>25.8047</v>
@@ -2352,13 +2452,16 @@
       <c r="AA33">
         <v>0.0175792558330067</v>
       </c>
-    </row>
-    <row r="34" spans="1:27">
+      <c r="AD33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>25.8047</v>
@@ -2417,13 +2520,16 @@
       <c r="AA34">
         <v>0.001612775764496</v>
       </c>
-    </row>
-    <row r="35" spans="1:27">
+      <c r="AD34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>25.5697</v>
@@ -2467,13 +2573,16 @@
       <c r="AA35">
         <v>8.97816140337296</v>
       </c>
-    </row>
-    <row r="36" spans="1:27">
+      <c r="AD35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C36">
         <v>25.5697</v>
@@ -2520,13 +2629,16 @@
       <c r="AA36">
         <v>0.013386038845317</v>
       </c>
-    </row>
-    <row r="37" spans="1:27">
+      <c r="AD36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37">
         <v>25.5697</v>
@@ -2573,13 +2685,16 @@
       <c r="AA37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:27">
+      <c r="AD37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38">
         <v>25.5697</v>
@@ -2626,13 +2741,16 @@
       <c r="AA38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:27">
+      <c r="AD38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C39">
         <v>25.5697</v>
@@ -2679,13 +2797,16 @@
       <c r="AA39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:27">
+      <c r="AD39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40">
         <v>25.5697</v>
@@ -2744,13 +2865,16 @@
       <c r="AA40">
         <v>0.0175792558330067</v>
       </c>
-    </row>
-    <row r="41" spans="1:27">
+      <c r="AD40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41">
         <v>25.5697</v>
@@ -2797,13 +2921,16 @@
       <c r="AA41">
         <v>0.0009676654586976</v>
       </c>
-    </row>
-    <row r="42" spans="1:27">
+      <c r="AD41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42">
         <v>25.5621</v>
@@ -2850,13 +2977,16 @@
       <c r="AA42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:27">
+      <c r="AD42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C43">
         <v>3.87</v>
@@ -2891,13 +3021,16 @@
       <c r="Z43">
         <v>8209.285187914516</v>
       </c>
-    </row>
-    <row r="44" spans="1:27">
+      <c r="AD43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44">
         <v>3.85</v>
@@ -2932,13 +3065,16 @@
       <c r="Z44">
         <v>9818.928308242972</v>
       </c>
-    </row>
-    <row r="45" spans="1:27">
+      <c r="AD44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C45">
         <v>3.45</v>
@@ -2973,13 +3109,16 @@
       <c r="Z45">
         <v>3826.718601958101</v>
       </c>
-    </row>
-    <row r="46" spans="1:27">
+      <c r="AD45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C46">
         <v>3.45</v>
@@ -3038,13 +3177,16 @@
       <c r="AA46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:27">
+      <c r="AD46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C47">
         <v>25.1706</v>
@@ -3088,13 +3230,16 @@
       <c r="AA47">
         <v>28.48049105796478</v>
       </c>
-    </row>
-    <row r="48" spans="1:27">
+      <c r="AD47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C48">
         <v>25.1706</v>
@@ -3138,13 +3283,16 @@
       <c r="AA48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:27">
+      <c r="AD48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C49">
         <v>25.1706</v>
@@ -3191,13 +3339,16 @@
       <c r="AA49">
         <v>0.0122570958101698</v>
       </c>
-    </row>
-    <row r="50" spans="1:27">
+      <c r="AD49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C50">
         <v>25.1706</v>
@@ -3244,13 +3395,16 @@
       <c r="AA50">
         <v>0.0899928876588785</v>
       </c>
-    </row>
-    <row r="51" spans="1:27">
+      <c r="AD50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C51">
         <v>25.1706</v>
@@ -3297,13 +3451,16 @@
       <c r="AA51">
         <v>0.0785421797309567</v>
       </c>
-    </row>
-    <row r="52" spans="1:27">
+      <c r="AD51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C52">
         <v>25.1706</v>
@@ -3362,13 +3519,16 @@
       <c r="AA52">
         <v>0.0070962133637825</v>
       </c>
-    </row>
-    <row r="53" spans="1:27">
+      <c r="AD52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L53">
         <v>13.79997500681053</v>
@@ -3411,6 +3571,9 @@
       </c>
       <c r="AA53">
         <v>0.0612854790508492</v>
+      </c>
+      <c r="AD53">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
